--- a/data/trans_orig/IP13_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Estudios-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (Tasa respuesta: 99,9%)</t>
+          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>4901</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>7098</v>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7098</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13235</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>11,45%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>11999</v>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9823</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>4839</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>15732</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>49777</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>54906</v>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>104683</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5875</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>54678</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49777</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>45338</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>62004</v>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>82,92%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>54906</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>116682</v>
+          <t>48769</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>58351</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>88,55%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>104683</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>97772</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>109755</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>89,72%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>22546</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54678</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>29616</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>52162</v>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62004</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>116682</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>606</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>437148</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17843</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>613</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>487003</v>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>1219</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>924151</v>
+          <t>12415</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27480</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>36433</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>27166</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>46293</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>642</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>459694</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>656</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>516619</v>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>1298</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>976313</v>
+          <t>6356</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>18572</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>15728</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>9632</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>24247</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>9991</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>437148</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>428081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>443677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>11703</v>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>93,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>487003</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>21693</v>
+          <t>477159</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>495577</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>924151</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>911057</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>936213</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>94,66%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>216</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>139560</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>459694</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>459694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>459694</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>223</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>170922</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>656</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>516619</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>310483</v>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>516619</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>976313</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>976313</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>976313</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>149551</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6290</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>237</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>182625</v>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>467</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>332176</v>
+          <t>6118</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18654</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>17154</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>11181</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>25532</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>37437</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3701</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>48417</v>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>839</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>85854</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>4539</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1721</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>9656</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>883</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>626486</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139560</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>133385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>143762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>910</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>712831</v>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>223</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>170922</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>1793</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>1339317</v>
+          <t>163321</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>175949</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>93,59%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>310483</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>301570</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>317064</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>93,47%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>941</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>663923</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>149551</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>761248</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>237</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>182625</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>1917</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>1425171</v>
+          <t>182625</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>182625</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,13 +2040,499 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>332176</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>332176</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>332176</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19110</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>37128</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26271</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47471</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>63411</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>51064</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>77459</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5908</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16993</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6848</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>19006</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>14698</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>31461</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>626486</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>615242</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>635977</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>712831</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>701590</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>724706</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1793</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1339317</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>1322658</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>1354171</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>663923</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>663923</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>663923</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>761248</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1425171</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1425171</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1425171</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1536,14 +2540,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP13_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>49166</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97772</t>
+          <t>98274</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109755</t>
+          <t>109680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>428081</t>
+          <t>428475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>443677</t>
+          <t>444965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>477159</t>
+          <t>475913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>495577</t>
+          <t>495314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>911057</t>
+          <t>911274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>936213</t>
+          <t>935391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>26583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133385</t>
+          <t>132676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143762</t>
+          <t>143508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>163839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175949</t>
+          <t>175734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301570</t>
+          <t>301325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317064</t>
+          <t>317098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>36312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>77434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,47 +2226,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31461</t>
+          <t>31232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>615242</t>
+          <t>615595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>635977</t>
+          <t>636115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>701590</t>
+          <t>699766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1322658</t>
+          <t>1322110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1354171</t>
+          <t>1354107</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12339</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6615</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5699</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49830</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53202</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>49777</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>45000</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>82,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54906</t>
+          <t>42155</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49166</t>
+          <t>38077</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>44581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>104683</t>
+          <t>91985</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>85487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109680</t>
+          <t>96516</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11070</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23491</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>17843</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11101</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25316</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>24717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,22 +1251,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>43679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5784</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16988</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4703</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9901</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1857</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9350</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>11025</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>6336</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19494</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23672</t>
+          <t>23700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>448268</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>438977</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>456213</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>437148</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>428475</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>444965</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>487003</t>
+          <t>409726</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>475913</t>
+          <t>401876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>495314</t>
+          <t>416285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>924151</t>
+          <t>857994</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>911274</t>
+          <t>845778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>935391</t>
+          <t>868155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10445</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3172</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>25741</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3701</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8817</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1858,67 +1858,67 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156561</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149331</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>161197</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>139560</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>132676</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143508</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>170922</t>
+          <t>139679</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163839</t>
+          <t>133455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175734</t>
+          <t>144325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>310483</t>
+          <t>296240</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301325</t>
+          <t>286952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317098</t>
+          <t>302726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167882</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182625</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332176</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34234</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44933</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19317</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36312</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51064</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77434</t>
+          <t>75809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>654660</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>641976</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>664532</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>883</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>626486</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>615595</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>636115</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>712831</t>
+          <t>591559</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>699766</t>
+          <t>580768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>723830</t>
+          <t>600587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1339317</t>
+          <t>1246220</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1322110</t>
+          <t>1230110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1354107</t>
+          <t>1260800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1425171</t>
+          <t>1328629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
